--- a/naver-place-crawler/results_nail/송파_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/송파_네일샵.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V337"/>
+  <dimension ref="A1:V392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -31659,39 +31659,39 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>뷰티룸JJHair&amp;Nail</t>
+          <t>마이네일봄</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>jjhair1125@naver.com</t>
+          <t>durrkd12@naver.com</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
-          <t>0507-1332-2023</t>
+          <t>0507-1361-3110</t>
         </is>
       </c>
       <c r="F336" t="inlineStr"/>
       <c r="G336" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 삼학사로 42 서진빌딩 2층</t>
+          <t>서울특별시 송파구 올림픽로 119 파인애플상가 2층 2A-68호 마이네일봄</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/beautyroomjj_nail</t>
+          <t>http://pf.kakao.com/_YJwJb</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
@@ -31712,7 +31712,7 @@
       <c r="M336" t="inlineStr"/>
       <c r="N336" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O336" t="inlineStr">
@@ -31721,13 +31721,13 @@
         </is>
       </c>
       <c r="P336" t="n">
-        <v>709</v>
+        <v>21</v>
       </c>
       <c r="Q336" t="n">
-        <v>506</v>
+        <v>8</v>
       </c>
       <c r="R336" t="n">
-        <v>1215</v>
+        <v>29</v>
       </c>
       <c r="S336" t="inlineStr">
         <is>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="T336" t="inlineStr">
         <is>
-          <t>1369954411</t>
+          <t>1291158509</t>
         </is>
       </c>
       <c r="U336" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1369954411</t>
+          <t>https://m.place.naver.com/place/1291158509</t>
         </is>
       </c>
       <c r="V336" t="inlineStr">
@@ -31753,39 +31753,35 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>인테리어디자인</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>올드앤틱디자인</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>morning6@naver.com</t>
-        </is>
-      </c>
+          <t>라니네일</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr"/>
       <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr">
         <is>
-          <t>0507-1327-8741</t>
+          <t>0507-1422-0232</t>
         </is>
       </c>
       <c r="F337" t="inlineStr"/>
       <c r="G337" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 오금로27길 50 7층 603호</t>
+          <t>서울특별시 송파구 동남로9길 35 1층</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>http://www.oldantique.co.kr</t>
+          <t>https://www.instagram.com/</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
@@ -31815,30 +31811,4972 @@
         </is>
       </c>
       <c r="P337" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q337" t="n">
+        <v>2</v>
+      </c>
+      <c r="R337" t="n">
+        <v>8</v>
+      </c>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T337" t="inlineStr">
+        <is>
+          <t>575008962</t>
+        </is>
+      </c>
+      <c r="U337" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/575008962</t>
+        </is>
+      </c>
+      <c r="V337" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>네일리샵</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>alfud3377@naver.com</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
+      <c r="E338" t="inlineStr"/>
+      <c r="F338" t="inlineStr"/>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 송파대로 141 르피에드 지하1층 B102호</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xixdxiexj</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr"/>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P338" t="n">
+        <v>126</v>
+      </c>
+      <c r="Q338" t="n">
+        <v>13</v>
+      </c>
+      <c r="R338" t="n">
+        <v>139</v>
+      </c>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T338" t="inlineStr">
+        <is>
+          <t>1576272319</t>
+        </is>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1576272319</t>
+        </is>
+      </c>
+      <c r="V338" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>유비네일하우스</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr"/>
+      <c r="D339" t="inlineStr"/>
+      <c r="E339" t="inlineStr"/>
+      <c r="F339" t="inlineStr"/>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 백제고분로48가길 20 1층 102호</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_cArun</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr"/>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P339" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q339" t="n">
+        <v>16</v>
+      </c>
+      <c r="R339" t="n">
+        <v>120</v>
+      </c>
+      <c r="S339" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T339" t="inlineStr">
+        <is>
+          <t>1810183068</t>
+        </is>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1810183068</t>
+        </is>
+      </c>
+      <c r="V339" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>네일온유 송파본점</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>nailonu_@naver.com</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr"/>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>0507-1369-1463</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr"/>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 송파대로36길 45 1층 102호</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail.on_u</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr"/>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P340" t="n">
+        <v>446</v>
+      </c>
+      <c r="Q340" t="n">
+        <v>12</v>
+      </c>
+      <c r="R340" t="n">
+        <v>458</v>
+      </c>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T340" t="inlineStr">
+        <is>
+          <t>1018108304</t>
+        </is>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1018108304</t>
+        </is>
+      </c>
+      <c r="V340" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>채채네일</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr"/>
+      <c r="D341" t="inlineStr"/>
+      <c r="E341" t="inlineStr"/>
+      <c r="F341" t="inlineStr"/>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 백제고분로28길 22 1층</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>http://instagram.com/chae_chae_nail</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr"/>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P341" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q341" t="n">
+        <v>5</v>
+      </c>
+      <c r="R341" t="n">
+        <v>8</v>
+      </c>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T341" t="inlineStr">
+        <is>
+          <t>1520243553</t>
+        </is>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1520243553</t>
+        </is>
+      </c>
+      <c r="V341" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>네일어게인</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr"/>
+      <c r="D342" t="inlineStr"/>
+      <c r="E342" t="inlineStr"/>
+      <c r="F342" t="inlineStr"/>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 가락로 254-1 우영빌딩 1층</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail.again</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr"/>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P342" t="n">
+        <v>142</v>
+      </c>
+      <c r="Q342" t="n">
+        <v>8</v>
+      </c>
+      <c r="R342" t="n">
+        <v>150</v>
+      </c>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T342" t="inlineStr">
+        <is>
+          <t>1598282079</t>
+        </is>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1598282079</t>
+        </is>
+      </c>
+      <c r="V342" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>오니엘 잠실점</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>pedibene_songpa@naver.com</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>0507-1488-1148</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr"/>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 가락로11길 15 2층</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/pedibene_songpa</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr"/>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P343" t="n">
+        <v>209</v>
+      </c>
+      <c r="Q343" t="n">
+        <v>25</v>
+      </c>
+      <c r="R343" t="n">
+        <v>234</v>
+      </c>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>1164480388</t>
+        </is>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1164480388</t>
+        </is>
+      </c>
+      <c r="V343" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>알리자</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr"/>
+      <c r="D344" t="inlineStr"/>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>0507-1384-4118</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr"/>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 마천로 72 1층 2호</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/alliza_nail/</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr"/>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P344" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q344" t="n">
+        <v>37</v>
+      </c>
+      <c r="R344" t="n">
+        <v>81</v>
+      </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>1691510859</t>
+        </is>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1691510859</t>
+        </is>
+      </c>
+      <c r="V344" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>네일두나</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr"/>
+      <c r="D345" t="inlineStr"/>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>0507-1326-8193</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr"/>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 올림픽로 119 파인애플상가 지하 1층 A158</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>http://instagram.com/doona136</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr"/>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P345" t="n">
+        <v>162</v>
+      </c>
+      <c r="Q345" t="n">
+        <v>8</v>
+      </c>
+      <c r="R345" t="n">
+        <v>170</v>
+      </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T345" t="inlineStr">
+        <is>
+          <t>1782672614</t>
+        </is>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1782672614</t>
+        </is>
+      </c>
+      <c r="V345" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>네일공방 잠실</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr"/>
+      <c r="D346" t="inlineStr"/>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>0507-1316-8407</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr"/>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 삼학사로13길 13 1층</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_VxfZxfK</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr"/>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P346" t="n">
+        <v>795</v>
+      </c>
+      <c r="Q346" t="n">
+        <v>136</v>
+      </c>
+      <c r="R346" t="n">
+        <v>931</v>
+      </c>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T346" t="inlineStr">
+        <is>
+          <t>1504627718</t>
+        </is>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1504627718</t>
+        </is>
+      </c>
+      <c r="V346" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>네일의 달</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr"/>
+      <c r="D347" t="inlineStr"/>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>0507-1361-4066</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr"/>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 오금로44길 18-1 103호 네일의 달</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_nailomoon/</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr"/>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P347" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q347" t="n">
         <v>1</v>
       </c>
-      <c r="Q337" t="n">
+      <c r="R347" t="n">
+        <v>14</v>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T347" t="inlineStr">
+        <is>
+          <t>1243575298</t>
+        </is>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1243575298</t>
+        </is>
+      </c>
+      <c r="V347" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>두손네일</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr"/>
+      <c r="D348" t="inlineStr"/>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>02-402-2898</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr"/>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 마천로 315 현대그린빌(아)101동</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>http://www.정현네일앤속눈썹.com/</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr"/>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P348" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q348" t="n">
+        <v>1</v>
+      </c>
+      <c r="R348" t="n">
+        <v>2</v>
+      </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>32284269</t>
+        </is>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/32284269</t>
+        </is>
+      </c>
+      <c r="V348" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>콩네일</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr"/>
+      <c r="D349" t="inlineStr"/>
+      <c r="E349" t="inlineStr"/>
+      <c r="F349" t="inlineStr"/>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 백제고분로39길 8</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr"/>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P349" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q349" t="n">
+        <v>5</v>
+      </c>
+      <c r="R349" t="n">
+        <v>35</v>
+      </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>87782234</t>
+        </is>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/87782234</t>
+        </is>
+      </c>
+      <c r="V349" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>네일하비오</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr"/>
+      <c r="D350" t="inlineStr"/>
+      <c r="E350" t="inlineStr"/>
+      <c r="F350" t="inlineStr"/>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 송파대로 111 108동107호</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr"/>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P350" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q350" t="n">
+        <v>0</v>
+      </c>
+      <c r="R350" t="n">
+        <v>2</v>
+      </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>1392190956</t>
+        </is>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1392190956</t>
+        </is>
+      </c>
+      <c r="V350" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>뷰티릿</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr"/>
+      <c r="D351" t="inlineStr"/>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>0507-1402-3020</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr"/>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 삼전로6길 9 102호 뷰티릿</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>http://instagram.com/beauti_lit</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr"/>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P351" t="n">
+        <v>340</v>
+      </c>
+      <c r="Q351" t="n">
+        <v>96</v>
+      </c>
+      <c r="R351" t="n">
+        <v>436</v>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>1978838119</t>
+        </is>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1978838119</t>
+        </is>
+      </c>
+      <c r="V351" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>네일리티</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr"/>
+      <c r="D352" t="inlineStr"/>
+      <c r="E352" t="inlineStr"/>
+      <c r="F352" t="inlineStr"/>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 백제고분로45길 38-9 이움레이크 203호</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/naility_art/</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr"/>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P352" t="n">
+        <v>157</v>
+      </c>
+      <c r="Q352" t="n">
+        <v>16</v>
+      </c>
+      <c r="R352" t="n">
+        <v>173</v>
+      </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>1351466685</t>
+        </is>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1351466685</t>
+        </is>
+      </c>
+      <c r="V352" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>미대살롱</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr"/>
+      <c r="D353" t="inlineStr"/>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>0507-1361-1012</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr"/>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 오금로11길 37 대명벨리온 2층</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/midaesalon_beauty</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr"/>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P353" t="n">
+        <v>251</v>
+      </c>
+      <c r="Q353" t="n">
+        <v>36</v>
+      </c>
+      <c r="R353" t="n">
+        <v>287</v>
+      </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>1506012175</t>
+        </is>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1506012175</t>
+        </is>
+      </c>
+      <c r="V353" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>제떼네일</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr"/>
+      <c r="D354" t="inlineStr"/>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>0507-1339-1228</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr"/>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 삼전로6길 15 1층</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jettenail</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr"/>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P354" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q354" t="n">
+        <v>1</v>
+      </c>
+      <c r="R354" t="n">
+        <v>47</v>
+      </c>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>1851320424</t>
+        </is>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1851320424</t>
+        </is>
+      </c>
+      <c r="V354" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>JINANAIL</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr"/>
+      <c r="D355" t="inlineStr"/>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>0507-1487-3232</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr"/>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 중대로 24 올림픽훼밀리타운 상가 1동 1층 123호</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jinaaanail</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr"/>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P355" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q355" t="n">
+        <v>7</v>
+      </c>
+      <c r="R355" t="n">
+        <v>10</v>
+      </c>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T355" t="inlineStr">
+        <is>
+          <t>1060415243</t>
+        </is>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1060415243</t>
+        </is>
+      </c>
+      <c r="V355" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>감성네일 잠실</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr"/>
+      <c r="D356" t="inlineStr"/>
+      <c r="E356" t="inlineStr"/>
+      <c r="F356" t="inlineStr"/>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 올림픽로12길 42-1 1층</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr"/>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P356" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q356" t="n">
+        <v>1</v>
+      </c>
+      <c r="R356" t="n">
+        <v>2</v>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T356" t="inlineStr">
+        <is>
+          <t>1369212193</t>
+        </is>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1369212193</t>
+        </is>
+      </c>
+      <c r="V356" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>미앤유</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr"/>
+      <c r="D357" t="inlineStr"/>
+      <c r="E357" t="inlineStr"/>
+      <c r="F357" t="inlineStr"/>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 올림픽로 145</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr"/>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P357" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q357" t="n">
+        <v>0</v>
+      </c>
+      <c r="R357" t="n">
+        <v>27</v>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>1892708845</t>
+        </is>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1892708845</t>
+        </is>
+      </c>
+      <c r="V357" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>엔오에프 잠실르엘점</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr"/>
+      <c r="D358" t="inlineStr"/>
+      <c r="E358" t="inlineStr"/>
+      <c r="F358" t="inlineStr"/>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 올림픽로 329 잠실르엘상가 322호</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nof_le_el</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr"/>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P358" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q358" t="n">
+        <v>1</v>
+      </c>
+      <c r="R358" t="n">
+        <v>9</v>
+      </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T358" t="inlineStr">
+        <is>
+          <t>2032908756</t>
+        </is>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2032908756</t>
+        </is>
+      </c>
+      <c r="V358" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>미나네일</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr"/>
+      <c r="D359" t="inlineStr"/>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>0507-1380-1368</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr"/>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 마천로 30 코오롱 종합상가 A동 206호 미나네일</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/kimmina_nail</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr"/>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P359" t="n">
+        <v>266</v>
+      </c>
+      <c r="Q359" t="n">
+        <v>32</v>
+      </c>
+      <c r="R359" t="n">
+        <v>298</v>
+      </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T359" t="inlineStr">
+        <is>
+          <t>1021524307</t>
+        </is>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1021524307</t>
+        </is>
+      </c>
+      <c r="V359" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>로제네일</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr"/>
+      <c r="D360" t="inlineStr"/>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>0507-1380-0667</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr"/>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 성내천로 232 1층</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rosee_nail__</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr"/>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P360" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q360" t="n">
+        <v>1</v>
+      </c>
+      <c r="R360" t="n">
+        <v>16</v>
+      </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T360" t="inlineStr">
+        <is>
+          <t>1393715425</t>
+        </is>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1393715425</t>
+        </is>
+      </c>
+      <c r="V360" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>손톱여왕</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr"/>
+      <c r="D361" t="inlineStr"/>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>02-3432-7789</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr"/>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 올림픽로12길 37</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr"/>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P361" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q361" t="n">
+        <v>0</v>
+      </c>
+      <c r="R361" t="n">
+        <v>32</v>
+      </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T361" t="inlineStr">
+        <is>
+          <t>1911773265</t>
+        </is>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1911773265</t>
+        </is>
+      </c>
+      <c r="V361" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>톤즈 네일앤뷰티</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr"/>
+      <c r="D362" t="inlineStr"/>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>0507-1355-9788</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr"/>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 석촌호수로12길 42 103호</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tonz_nail_</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr"/>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P362" t="n">
+        <v>654</v>
+      </c>
+      <c r="Q362" t="n">
+        <v>21</v>
+      </c>
+      <c r="R362" t="n">
+        <v>675</v>
+      </c>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T362" t="inlineStr">
+        <is>
+          <t>1308025494</t>
+        </is>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1308025494</t>
+        </is>
+      </c>
+      <c r="V362" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>모제네일</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr"/>
+      <c r="D363" t="inlineStr"/>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>0507-1362-4499</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr"/>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 백제고분로28길 10 104호</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/morzenail</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr"/>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P363" t="n">
+        <v>403</v>
+      </c>
+      <c r="Q363" t="n">
+        <v>31</v>
+      </c>
+      <c r="R363" t="n">
+        <v>434</v>
+      </c>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T363" t="inlineStr">
+        <is>
+          <t>1073200952</t>
+        </is>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1073200952</t>
+        </is>
+      </c>
+      <c r="V363" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>나쯔네일</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr"/>
+      <c r="D364" t="inlineStr"/>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>0507-1493-8188</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr"/>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 백제고분로45길 11 렉스프라자 401호</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_wSDgxj</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr"/>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P364" t="n">
+        <v>427</v>
+      </c>
+      <c r="Q364" t="n">
+        <v>5</v>
+      </c>
+      <c r="R364" t="n">
+        <v>432</v>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T364" t="inlineStr">
+        <is>
+          <t>1203653870</t>
+        </is>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1203653870</t>
+        </is>
+      </c>
+      <c r="V364" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>네일그리다</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>nail_greeda_91@naver.com</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr"/>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>0507-1471-7786</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr"/>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 송이로28길 26 1층 네일그리다</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/greeda_som</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr"/>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P365" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q365" t="n">
+        <v>160</v>
+      </c>
+      <c r="R365" t="n">
+        <v>228</v>
+      </c>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T365" t="inlineStr">
+        <is>
+          <t>1237801664</t>
+        </is>
+      </c>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1237801664</t>
+        </is>
+      </c>
+      <c r="V365" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>노아네일&amp;패디플래닝</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr"/>
+      <c r="D366" t="inlineStr"/>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>0507-1468-8813</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr"/>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 올림픽로35길 112 B동 3층 19-1호</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/svEj2eaf</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr"/>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P366" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q366" t="n">
+        <v>6</v>
+      </c>
+      <c r="R366" t="n">
+        <v>55</v>
+      </c>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T366" t="inlineStr">
+        <is>
+          <t>1430868743</t>
+        </is>
+      </c>
+      <c r="U366" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1430868743</t>
+        </is>
+      </c>
+      <c r="V366" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>네일스토리</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr"/>
+      <c r="D367" t="inlineStr"/>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>0507-1406-4179</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr"/>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 올림픽로 119 지하1층 82~83호</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_nailstory</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr"/>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P367" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q367" t="n">
+        <v>33</v>
+      </c>
+      <c r="R367" t="n">
+        <v>91</v>
+      </c>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T367" t="inlineStr">
+        <is>
+          <t>20955373</t>
+        </is>
+      </c>
+      <c r="U367" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20955373</t>
+        </is>
+      </c>
+      <c r="V367" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>여우손톱</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr"/>
+      <c r="D368" t="inlineStr"/>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>0507-1347-9099</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr"/>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 가락로39길 21 1층(방이동)</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/foxnail_jamsil?igsh=YWg4cXUwdzF0eWNr</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr"/>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P368" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q368" t="n">
+        <v>0</v>
+      </c>
+      <c r="R368" t="n">
+        <v>16</v>
+      </c>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T368" t="inlineStr">
+        <is>
+          <t>1284116397</t>
+        </is>
+      </c>
+      <c r="U368" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1284116397</t>
+        </is>
+      </c>
+      <c r="V368" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>포쉬네일</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr"/>
+      <c r="D369" t="inlineStr"/>
+      <c r="E369" t="inlineStr"/>
+      <c r="F369" t="inlineStr"/>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 충민로 66 현대시티몰가든파이브점몰관2F</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr"/>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P369" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q369" t="n">
+        <v>0</v>
+      </c>
+      <c r="R369" t="n">
+        <v>0</v>
+      </c>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T369" t="inlineStr">
+        <is>
+          <t>1864806555</t>
+        </is>
+      </c>
+      <c r="U369" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1864806555</t>
+        </is>
+      </c>
+      <c r="V369" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>르엘네일</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr"/>
+      <c r="D370" t="inlineStr"/>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>0507-1366-0146</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr"/>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 오금로11길 55 현대주상복합빌딩 2층 213-32호</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/socu3d5g</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr"/>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P370" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q370" t="n">
+        <v>1</v>
+      </c>
+      <c r="R370" t="n">
+        <v>64</v>
+      </c>
+      <c r="S370" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T370" t="inlineStr">
+        <is>
+          <t>1998649445</t>
+        </is>
+      </c>
+      <c r="U370" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1998649445</t>
+        </is>
+      </c>
+      <c r="V370" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>마오네일</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr"/>
+      <c r="D371" t="inlineStr"/>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>0507-1322-4850</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr"/>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 오금로11길 45 사보이시티 잠실, 205호 마오네일</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/mao_nail_</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr"/>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P371" t="n">
+        <v>433</v>
+      </c>
+      <c r="Q371" t="n">
+        <v>25</v>
+      </c>
+      <c r="R371" t="n">
+        <v>458</v>
+      </c>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T371" t="inlineStr">
+        <is>
+          <t>1032214871</t>
+        </is>
+      </c>
+      <c r="U371" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1032214871</t>
+        </is>
+      </c>
+      <c r="V371" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>네일프렌들리</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr"/>
+      <c r="D372" t="inlineStr"/>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>02-429-0000</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr"/>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 법원로11길 11 현대지식산업센터 1-1 A동 2층 214호</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_mkEfb</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr"/>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P372" t="n">
+        <v>245</v>
+      </c>
+      <c r="Q372" t="n">
+        <v>48</v>
+      </c>
+      <c r="R372" t="n">
+        <v>293</v>
+      </c>
+      <c r="S372" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T372" t="inlineStr">
+        <is>
+          <t>1718199584</t>
+        </is>
+      </c>
+      <c r="U372" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1718199584</t>
+        </is>
+      </c>
+      <c r="V372" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>리오떼 네일</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr"/>
+      <c r="D373" t="inlineStr"/>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>0507-1481-8260</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr"/>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 올림픽로34길 6 201호</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_NGLWb</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr"/>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P373" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q373" t="n">
+        <v>100</v>
+      </c>
+      <c r="R373" t="n">
+        <v>101</v>
+      </c>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T373" t="inlineStr">
+        <is>
+          <t>1151759698</t>
+        </is>
+      </c>
+      <c r="U373" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1151759698</t>
+        </is>
+      </c>
+      <c r="V373" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>네일바이슈</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr"/>
+      <c r="D374" t="inlineStr"/>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>0507-1362-1008</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr"/>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 송이로6길 3 1층</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_KxfxcQT</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr"/>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P374" t="n">
+        <v>139</v>
+      </c>
+      <c r="Q374" t="n">
+        <v>13</v>
+      </c>
+      <c r="R374" t="n">
+        <v>152</v>
+      </c>
+      <c r="S374" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T374" t="inlineStr">
+        <is>
+          <t>1691077579</t>
+        </is>
+      </c>
+      <c r="U374" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1691077579</t>
+        </is>
+      </c>
+      <c r="V374" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>안녕제이</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr"/>
+      <c r="D375" t="inlineStr"/>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>0507-1351-4050</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr"/>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 석촌호수로 298 대우레이크월드 205호</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/hello_j_nail</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr"/>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P375" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q375" t="n">
+        <v>34</v>
+      </c>
+      <c r="R375" t="n">
+        <v>69</v>
+      </c>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T375" t="inlineStr">
+        <is>
+          <t>1575542332</t>
+        </is>
+      </c>
+      <c r="U375" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1575542332</t>
+        </is>
+      </c>
+      <c r="V375" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>지네일 위례점</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr"/>
+      <c r="D376" t="inlineStr"/>
+      <c r="E376" t="inlineStr"/>
+      <c r="F376" t="inlineStr"/>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 위례광장로 136 상가3동 C-110호</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gnail_wirye</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr"/>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P376" t="n">
+        <v>1256</v>
+      </c>
+      <c r="Q376" t="n">
+        <v>75</v>
+      </c>
+      <c r="R376" t="n">
+        <v>1331</v>
+      </c>
+      <c r="S376" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T376" t="inlineStr">
+        <is>
+          <t>1047579875</t>
+        </is>
+      </c>
+      <c r="U376" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1047579875</t>
+        </is>
+      </c>
+      <c r="V376" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>글래드네일</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>glad_beauty@naver.com</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr"/>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>0507-1379-8741</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr"/>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 가락로 90 2층 글래드네일</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/glad_beauty</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr"/>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P377" t="n">
+        <v>285</v>
+      </c>
+      <c r="Q377" t="n">
+        <v>3</v>
+      </c>
+      <c r="R377" t="n">
+        <v>288</v>
+      </c>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T377" t="inlineStr">
+        <is>
+          <t>1172165464</t>
+        </is>
+      </c>
+      <c r="U377" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1172165464</t>
+        </is>
+      </c>
+      <c r="V377" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>하나네일</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr"/>
+      <c r="D378" t="inlineStr"/>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>02-402-9427</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr"/>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 문정로 83 문정래미안상가 1층 122호</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr"/>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P378" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q378" t="n">
+        <v>2</v>
+      </c>
+      <c r="R378" t="n">
         <v>4</v>
       </c>
-      <c r="R337" t="n">
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T378" t="inlineStr">
+        <is>
+          <t>1085758230</t>
+        </is>
+      </c>
+      <c r="U378" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1085758230</t>
+        </is>
+      </c>
+      <c r="V378" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>에뜨로뷰티</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr"/>
+      <c r="D379" t="inlineStr"/>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>0507-1330-2568</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr"/>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 양산로 12 세신훼미리타운 214호</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/ettr.o_beauty</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M379" t="inlineStr"/>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P379" t="n">
+        <v>516</v>
+      </c>
+      <c r="Q379" t="n">
+        <v>13</v>
+      </c>
+      <c r="R379" t="n">
+        <v>529</v>
+      </c>
+      <c r="S379" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T379" t="inlineStr">
+        <is>
+          <t>1525041514</t>
+        </is>
+      </c>
+      <c r="U379" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1525041514</t>
+        </is>
+      </c>
+      <c r="V379" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>유나네일</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr"/>
+      <c r="D380" t="inlineStr"/>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>02-3401-1777</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr"/>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 오금로57길 3-4 1층</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr"/>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P380" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q380" t="n">
+        <v>4</v>
+      </c>
+      <c r="R380" t="n">
+        <v>13</v>
+      </c>
+      <c r="S380" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T380" t="inlineStr">
+        <is>
+          <t>1424470792</t>
+        </is>
+      </c>
+      <c r="U380" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1424470792</t>
+        </is>
+      </c>
+      <c r="V380" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>디에고푸스 위례점 네일어베인</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>kaj5677@naver.com</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr"/>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>0507-1352-8131</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr"/>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 위례광장로 170 힐스테이트몰 A동 1층 네일어베인</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>http://instagram.com/nail_urbane</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr"/>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P381" t="n">
+        <v>1513</v>
+      </c>
+      <c r="Q381" t="n">
+        <v>267</v>
+      </c>
+      <c r="R381" t="n">
+        <v>1780</v>
+      </c>
+      <c r="S381" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T381" t="inlineStr">
+        <is>
+          <t>1592902531</t>
+        </is>
+      </c>
+      <c r="U381" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1592902531</t>
+        </is>
+      </c>
+      <c r="V381" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>네일리고</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>alth1690@naver.com</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr"/>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>0507-1328-1690</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr"/>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 중대로 135 지하1층 네일리고(it벤처타워)</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_leego</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr"/>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P382" t="n">
+        <v>363</v>
+      </c>
+      <c r="Q382" t="n">
+        <v>197</v>
+      </c>
+      <c r="R382" t="n">
+        <v>560</v>
+      </c>
+      <c r="S382" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T382" t="inlineStr">
+        <is>
+          <t>1146667660</t>
+        </is>
+      </c>
+      <c r="U382" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1146667660</t>
+        </is>
+      </c>
+      <c r="V382" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>에또알네일 잠실새내점</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>sol17-@naver.com</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr"/>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>0507-1395-1385</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr"/>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 백제고분로7길 41 3층 304호</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/etoilee_nail</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr"/>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P383" t="n">
+        <v>694</v>
+      </c>
+      <c r="Q383" t="n">
+        <v>59</v>
+      </c>
+      <c r="R383" t="n">
+        <v>753</v>
+      </c>
+      <c r="S383" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T383" t="inlineStr">
+        <is>
+          <t>1633713970</t>
+        </is>
+      </c>
+      <c r="U383" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1633713970</t>
+        </is>
+      </c>
+      <c r="V383" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>셀리네일샾</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>loo1823@naver.com</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr"/>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>0507-1375-8589</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr"/>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 백제고분로34길 7</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr"/>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P384" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q384" t="n">
+        <v>173</v>
+      </c>
+      <c r="R384" t="n">
+        <v>202</v>
+      </c>
+      <c r="S384" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T384" t="inlineStr">
+        <is>
+          <t>955277428</t>
+        </is>
+      </c>
+      <c r="U384" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/955277428</t>
+        </is>
+      </c>
+      <c r="V384" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>러디네일</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>nanaday_1@naver.com</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr"/>
+      <c r="E385" t="inlineStr"/>
+      <c r="F385" t="inlineStr"/>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 문정로1길 15 1층 러디네일</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_AxcSxcG</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr"/>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P385" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q385" t="n">
+        <v>11</v>
+      </c>
+      <c r="R385" t="n">
+        <v>41</v>
+      </c>
+      <c r="S385" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T385" t="inlineStr">
+        <is>
+          <t>1948598349</t>
+        </is>
+      </c>
+      <c r="U385" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1948598349</t>
+        </is>
+      </c>
+      <c r="V385" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>바니앤루나</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>jopd2737@naver.com</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr"/>
+      <c r="E386" t="inlineStr"/>
+      <c r="F386" t="inlineStr"/>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 올림픽로 119 B1층 B-19호</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailart_ara</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr"/>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P386" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q386" t="n">
+        <v>0</v>
+      </c>
+      <c r="R386" t="n">
+        <v>34</v>
+      </c>
+      <c r="S386" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T386" t="inlineStr">
+        <is>
+          <t>734980043</t>
+        </is>
+      </c>
+      <c r="U386" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/734980043</t>
+        </is>
+      </c>
+      <c r="V386" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>유니원네일</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>twoy0706@naver.com</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr"/>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>0507-1317-9757</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr"/>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 올림픽로45길 11 상가동 101호</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/u.nee_1_nail</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr"/>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P387" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q387" t="n">
+        <v>164</v>
+      </c>
+      <c r="R387" t="n">
+        <v>165</v>
+      </c>
+      <c r="S387" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T387" t="inlineStr">
+        <is>
+          <t>1867492796</t>
+        </is>
+      </c>
+      <c r="U387" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1867492796</t>
+        </is>
+      </c>
+      <c r="V387" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>아이니 네일</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr"/>
+      <c r="D388" t="inlineStr"/>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>0507-1479-3747</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr"/>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 올림픽로12길 25 1층 101호</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/aini_nail</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr"/>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P388" t="n">
+        <v>144</v>
+      </c>
+      <c r="Q388" t="n">
+        <v>2</v>
+      </c>
+      <c r="R388" t="n">
+        <v>146</v>
+      </c>
+      <c r="S388" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T388" t="inlineStr">
+        <is>
+          <t>2020541149</t>
+        </is>
+      </c>
+      <c r="U388" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2020541149</t>
+        </is>
+      </c>
+      <c r="V388" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>네일 진 아뜰리에</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr"/>
+      <c r="D389" t="inlineStr"/>
+      <c r="E389" t="inlineStr"/>
+      <c r="F389" t="inlineStr"/>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 백제고분로42길 35-1 103호</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>http://instagram.com/nail_jin_atelier</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr"/>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P389" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q389" t="n">
+        <v>4</v>
+      </c>
+      <c r="R389" t="n">
+        <v>33</v>
+      </c>
+      <c r="S389" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T389" t="inlineStr">
+        <is>
+          <t>1657175756</t>
+        </is>
+      </c>
+      <c r="U389" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1657175756</t>
+        </is>
+      </c>
+      <c r="V389" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>카라네일</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr"/>
+      <c r="D390" t="inlineStr"/>
+      <c r="E390" t="inlineStr"/>
+      <c r="F390" t="inlineStr"/>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 송이로15길 42 1층</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kara_nail_81</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr"/>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P390" t="n">
+        <v>108</v>
+      </c>
+      <c r="Q390" t="n">
+        <v>12</v>
+      </c>
+      <c r="R390" t="n">
+        <v>120</v>
+      </c>
+      <c r="S390" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T390" t="inlineStr">
+        <is>
+          <t>31119724</t>
+        </is>
+      </c>
+      <c r="U390" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31119724</t>
+        </is>
+      </c>
+      <c r="V390" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>뷰티룸JJHair&amp;Nail</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>jjhair1125@naver.com</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr"/>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>0507-1332-2023</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr"/>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 삼학사로 42 서진빌딩 2층</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/beautyroomjj_nail</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr"/>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P391" t="n">
+        <v>709</v>
+      </c>
+      <c r="Q391" t="n">
+        <v>506</v>
+      </c>
+      <c r="R391" t="n">
+        <v>1215</v>
+      </c>
+      <c r="S391" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T391" t="inlineStr">
+        <is>
+          <t>1369954411</t>
+        </is>
+      </c>
+      <c r="U391" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1369954411</t>
+        </is>
+      </c>
+      <c r="V391" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>인테리어디자인</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>올드앤틱디자인</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>morning6@naver.com</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr"/>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>0507-1327-8741</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr"/>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 오금로27길 50 7층 603호</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>http://www.oldantique.co.kr</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr"/>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P392" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q392" t="n">
+        <v>4</v>
+      </c>
+      <c r="R392" t="n">
         <v>5</v>
       </c>
-      <c r="S337" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T337" t="inlineStr">
+      <c r="S392" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T392" t="inlineStr">
         <is>
           <t>1286264559</t>
         </is>
       </c>
-      <c r="U337" t="inlineStr">
+      <c r="U392" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1286264559</t>
         </is>
       </c>
-      <c r="V337" t="inlineStr">
+      <c r="V392" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_nail/송파_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/송파_네일샵.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V389"/>
+  <dimension ref="A1:V391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -36515,34 +36515,34 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>뷰티룸JJHair&amp;Nail</t>
+          <t>더바른네일 방이동 송파나루점</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>jjhair1125@naver.com</t>
+          <t>nail_the_barun@naver.com</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr">
         <is>
-          <t>0507-1332-2023</t>
+          <t>0507-1475-3327</t>
         </is>
       </c>
       <c r="F388" t="inlineStr"/>
       <c r="G388" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 삼학사로 42 서진빌딩 2층</t>
+          <t>서울특별시 송파구 백제고분로48길 13 2층 202호</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/beautyroomjj_nail</t>
+          <t>http://instagram.com/nail_the_barun</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -36577,13 +36577,13 @@
         </is>
       </c>
       <c r="P388" t="n">
-        <v>709</v>
+        <v>1119</v>
       </c>
       <c r="Q388" t="n">
-        <v>506</v>
+        <v>65</v>
       </c>
       <c r="R388" t="n">
-        <v>1215</v>
+        <v>1184</v>
       </c>
       <c r="S388" t="inlineStr">
         <is>
@@ -36592,12 +36592,12 @@
       </c>
       <c r="T388" t="inlineStr">
         <is>
-          <t>1369954411</t>
+          <t>1141810855</t>
         </is>
       </c>
       <c r="U388" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1369954411</t>
+          <t>https://m.place.naver.com/place/1141810855</t>
         </is>
       </c>
       <c r="V388" t="inlineStr">
@@ -36609,34 +36609,34 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>인테리어디자인</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>올드앤틱디자인</t>
+          <t>유니원네일</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>morning6@naver.com</t>
+          <t>twoy0706@naver.com</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr">
         <is>
-          <t>0507-1327-8741</t>
+          <t>0507-1317-9757</t>
         </is>
       </c>
       <c r="F389" t="inlineStr"/>
       <c r="G389" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 오금로27길 50 7층 603호</t>
+          <t>서울특별시 송파구 올림픽로45길 11 상가동 101호</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>http://www.oldantique.co.kr</t>
+          <t>http://www.instagram.com/u.nee_1_nail</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -36651,7 +36651,7 @@
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
@@ -36674,27 +36674,215 @@
         <v>1</v>
       </c>
       <c r="Q389" t="n">
+        <v>164</v>
+      </c>
+      <c r="R389" t="n">
+        <v>165</v>
+      </c>
+      <c r="S389" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T389" t="inlineStr">
+        <is>
+          <t>1867492796</t>
+        </is>
+      </c>
+      <c r="U389" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1867492796</t>
+        </is>
+      </c>
+      <c r="V389" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>뷰티룸JJHair&amp;Nail</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>jjhair1125@naver.com</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr"/>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>0507-1332-2023</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr"/>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 삼학사로 42 서진빌딩 2층</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/beautyroomjj_nail</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr"/>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P390" t="n">
+        <v>709</v>
+      </c>
+      <c r="Q390" t="n">
+        <v>506</v>
+      </c>
+      <c r="R390" t="n">
+        <v>1215</v>
+      </c>
+      <c r="S390" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T390" t="inlineStr">
+        <is>
+          <t>1369954411</t>
+        </is>
+      </c>
+      <c r="U390" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1369954411</t>
+        </is>
+      </c>
+      <c r="V390" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>인테리어디자인</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>올드앤틱디자인</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>morning6@naver.com</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr"/>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>0507-1327-8741</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr"/>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>서울특별시 송파구 오금로27길 50 7층 603호</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>http://www.oldantique.co.kr</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr"/>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P391" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q391" t="n">
         <v>4</v>
       </c>
-      <c r="R389" t="n">
+      <c r="R391" t="n">
         <v>5</v>
       </c>
-      <c r="S389" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T389" t="inlineStr">
+      <c r="S391" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T391" t="inlineStr">
         <is>
           <t>1286264559</t>
         </is>
       </c>
-      <c r="U389" t="inlineStr">
+      <c r="U391" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1286264559</t>
         </is>
       </c>
-      <c r="V389" t="inlineStr">
+      <c r="V391" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
